--- a/docs/downloads/04/tbl_cm_act_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,14 +384,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>12.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -402,14 +402,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="4">
@@ -420,7 +420,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C4">
@@ -438,14 +438,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>25.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="6">
@@ -456,32 +456,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>2.1</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>13.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8">
@@ -492,14 +492,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>6.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -510,14 +504,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C9">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D9">
-        <v>55.3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -528,14 +522,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C10">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="D10">
-        <v>23.6</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="11">
@@ -546,50 +540,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.8</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C12">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>16.1</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>2.2</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -600,14 +582,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C14">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>68.59999999999999</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="15">
@@ -618,86 +600,80 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>18</v>
-      </c>
-      <c r="D15">
-        <v>13.1</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C16">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="D16">
-        <v>31</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C18">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="D18">
-        <v>53.4</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="20">
@@ -708,74 +684,74 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D20">
-        <v>0.9</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C21">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>17.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C22">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D22">
-        <v>4.2</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C23">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>58.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -784,28 +760,130 @@
         </is>
       </c>
       <c r="C24">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>18.3</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Marovoay - Maroala</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Marovoay - Tous</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>5</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>35</v>
+      </c>
+      <c r="D26">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>38</v>
+      </c>
+      <c r="D27">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>304</v>
+      </c>
+      <c r="D28">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>25</v>
+      </c>
+      <c r="D29">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>95</v>
+      </c>
+      <c r="D30">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>22</v>
+      </c>
+      <c r="D31">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_act_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -625,7 +625,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">

--- a/docs/downloads/04/tbl_cm_act_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -456,14 +456,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>25.9</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -474,26 +468,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D7">
-        <v>4.9</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bepako</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -504,14 +504,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>13</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -522,14 +516,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C10">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>55.3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -540,8 +534,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>68</v>
+      </c>
+      <c r="D11">
+        <v>55.3</v>
       </c>
     </row>
     <row r="12">
@@ -552,14 +552,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>29</v>
-      </c>
-      <c r="D12">
-        <v>23.6</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -570,26 +564,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>23.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
-      <c r="D14">
-        <v>4.4</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -600,8 +594,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>4.4</v>
       </c>
     </row>
     <row r="16">
@@ -612,14 +612,8 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>94</v>
-      </c>
-      <c r="D16">
-        <v>68.59999999999999</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -630,14 +624,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="D17">
-        <v>5.1</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -648,14 +642,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="C18">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>13.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="19">
@@ -666,50 +660,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>8</v>
-      </c>
-      <c r="D19">
-        <v>5.8</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20">
-        <v>17.2</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>9.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="22">
@@ -720,14 +708,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C22">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D22">
-        <v>53.4</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="23">
@@ -738,14 +726,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="24">
@@ -756,14 +744,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="C24">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D24">
-        <v>9.5</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="25">
@@ -774,62 +762,56 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25">
+        <v>6.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>35</v>
-      </c>
-      <c r="D26">
-        <v>6.7</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="C27">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>304</v>
-      </c>
-      <c r="D28">
-        <v>58.6</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -840,14 +822,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="C29">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D29">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="30">
@@ -858,14 +840,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="C30">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="D30">
-        <v>18.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="31">
@@ -876,14 +858,86 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>304</v>
+      </c>
+      <c r="D31">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>25</v>
+      </c>
+      <c r="D32">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>95</v>
+      </c>
+      <c r="D34">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Services &amp; Autres</t>
         </is>
       </c>
-      <c r="C31">
-        <v>22</v>
-      </c>
-      <c r="D31">
-        <v>4.2</v>
+      <c r="C35">
+        <v>17</v>
+      </c>
+      <c r="D35">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
